--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -723,60 +731,64 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +802,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>2/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +850,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +860,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +917,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +953,911 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1011,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1072,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1244,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1405,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1515,12 +1531,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1631,7 +1647,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1742,7 +1758,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1819,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1852,12 +1868,801 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1108,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,17 +1169,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1185,13 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1229,24 +1237,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1421,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,37 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1647,7 +1659,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1758,7 +1770,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1873,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1988,7 +2000,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2099,7 +2111,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2214,7 +2226,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2325,7 +2337,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2398,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2430,13 +2442,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2513,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2547,7 +2563,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2657,12 +2673,460 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1346,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,17 +1407,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1423,13 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1467,24 +1475,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1494,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1687,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1720,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1946,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1985,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2061,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2172,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2287,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2452,7 +2468,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2529,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2640,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2866,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2977,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3005,13 +3021,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3092,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3121,12 +3141,468 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,17 +1875,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1891,12 +1895,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1929,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1962,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1986,17 +1994,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2006,7 +2014,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2044,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2077,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2101,33 +2113,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2242,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2381,32 +2397,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2414,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2438,17 +2458,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2458,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2496,32 +2516,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2529,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2553,33 +2577,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2679,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2694,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2794,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2866,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2905,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2977,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3031,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3131,7 +3159,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3146,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3346,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3362,12 +3390,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3433,7 +3461,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3487,7 +3515,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3495,22 +3523,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3543,12 +3571,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3562,47 +3590,955 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,13 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,18 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2607,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,32 +2980,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3005,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3029,37 +3041,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,32 +3214,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3235,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3259,17 +3275,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3279,13 +3295,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3385,7 +3405,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3461,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3500,7 +3520,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3543,32 +3563,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3576,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3600,17 +3624,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3620,17 +3644,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3658,32 +3682,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3691,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3715,37 +3743,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3773,32 +3801,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3806,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3830,33 +3862,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3956,7 +3992,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4032,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4086,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4186,7 +4222,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4201,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4542,6 +4578,811 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>84.5</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,14 +2481,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>84.5</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,18 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,7 +3060,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3071,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,17 +3180,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3309,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3409,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3420,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3525,17 +3529,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3811,24 +3815,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3838,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3887,12 +3891,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3920,32 +3924,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3953,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3977,17 +3985,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3997,17 +4005,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4043,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4068,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4092,17 +4104,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4112,17 +4124,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4265,32 +4277,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4298,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4322,33 +4338,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4376,32 +4396,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4409,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4433,17 +4457,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4453,17 +4477,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4563,7 +4587,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4574,7 +4598,7 @@
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -4602,32 +4626,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4635,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4659,17 +4687,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4679,17 +4707,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4789,7 +4817,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4804,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4919,7 +4947,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4980,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5024,17 +5052,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5134,7 +5162,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5149,7 +5177,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5264,7 +5292,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5374,12 +5402,694 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,32 +4860,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4893,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4917,17 +4921,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4937,12 +4941,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -4975,32 +4979,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5008,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5040,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,17 +5060,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5090,32 +5098,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5123,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5147,17 +5159,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5167,12 +5179,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5205,32 +5217,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5238,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5262,17 +5278,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5282,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5392,7 +5408,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5407,7 +5423,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5441,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5482,7 +5498,7 @@
       <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5579,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5618,7 +5634,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5694,7 +5710,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,7 +5825,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5848,7 +5864,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5920,7 +5936,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5964,12 +5980,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6035,7 +6051,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6093,6 +6109,577 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,13 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,17 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,17 +3064,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3255,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3309,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3524,7 +3528,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3539,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,7 +3647,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3658,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,12 +3890,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4362,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4592,13 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,7 +4710,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4717,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4817,17 +4825,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5070,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5182,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,32 +5344,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5369,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5393,17 +5405,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5413,12 +5425,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5451,32 +5463,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -5484,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,17 +5524,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5528,13 +5544,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5562,32 +5582,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5595,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5619,17 +5643,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5639,17 +5663,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5677,32 +5701,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5710,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5734,32 +5762,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5825,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5903,32 +5931,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5936,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5960,37 +5992,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6090,7 +6122,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6105,7 +6137,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6210,12 +6242,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6281,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6320,7 +6352,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6335,7 +6367,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6428,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6440,17 +6472,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6543,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6565,7 +6597,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6573,22 +6605,22 @@
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6621,12 +6653,12 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6665,18 +6697,593 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr"/>
-      <c r="AC53" s="2" t="inlineStr">
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5663,17 +5663,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6050,32 +6050,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6083,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6107,17 +6111,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6127,12 +6131,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6165,32 +6169,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -6198,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6222,32 +6230,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6280,32 +6288,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6313,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6337,17 +6349,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6357,12 +6369,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6395,32 +6407,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6428,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6452,17 +6468,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6472,17 +6488,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6582,7 +6598,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6658,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6697,7 +6713,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6712,7 +6728,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6746,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6773,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6787,7 +6803,7 @@
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6884,7 +6900,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,7 +7015,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7043,12 +7059,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7114,7 +7130,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7163,7 +7179,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7176,22 +7192,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7224,12 +7240,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7243,47 +7259,622 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>78.5</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>1/15</t>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,13 +5897,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6087,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6141,7 +6145,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6325,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,24 +6421,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6444,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6493,12 +6497,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6641,32 +6645,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6674,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6698,17 +6706,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6718,17 +6726,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6756,32 +6764,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -6789,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6813,17 +6825,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6833,13 +6845,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6916,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6954,7 +6970,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7031,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7069,7 +7085,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,7 +7333,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -7360,7 +7376,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7374,7 +7390,7 @@
       <c r="T59" s="2" t="inlineStr"/>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
@@ -7475,7 +7491,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7606,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,7 +7721,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7767,22 +7783,22 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7815,12 +7831,12 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7834,47 +7850,162 @@
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr">
         <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
           <t>16:01</t>
         </is>
       </c>
-      <c r="V63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr">
+      <c r="W64" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X63" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z63" s="2" t="inlineStr">
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>11/15</t>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,22 +3064,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,22 +4825,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5182,22 +5182,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5777,22 +5777,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,17 +6135,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,17 +6373,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6530,32 +6530,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6563,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6587,17 +6591,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6607,17 +6611,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6645,36 +6649,32 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6706,17 +6706,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6726,17 +6726,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6774,24 +6774,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6883,32 +6883,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6916,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6940,37 +6944,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6998,32 +7002,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7031,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7055,17 +7063,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7075,17 +7083,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7113,32 +7121,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7146,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7170,37 +7182,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7300,7 +7312,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7315,7 +7327,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7343,32 +7355,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7376,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7400,17 +7416,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7420,17 +7436,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7507,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7530,7 +7546,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7606,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7660,7 +7676,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7765,17 +7781,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7852,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7898,22 +7914,22 @@
       <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7946,12 +7962,12 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8000,12 +8016,1047 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
           <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>85.2</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,14 +2481,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>85.2</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,22 +3528,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,22 +4357,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,17 +5068,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,22 +5658,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>85.2</t>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6249,17 +6249,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6487,22 +6487,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6606,22 +6606,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6721,22 +6721,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7078,14 +7078,14 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>85.2</t>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,32 +7240,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7273,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7297,17 +7301,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7317,17 +7321,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7365,24 +7369,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7392,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7431,7 +7435,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7441,7 +7445,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7474,32 +7478,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7507,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7531,17 +7539,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7551,17 +7559,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7589,32 +7597,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -7622,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7646,32 +7658,32 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7704,32 +7716,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7737,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7761,37 +7777,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7819,32 +7835,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7852,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7876,37 +7896,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7934,32 +7954,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7967,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7991,37 +8015,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8049,32 +8073,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -8082,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8106,37 +8134,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8225,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8251,7 +8279,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8340,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,7 +8455,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8481,7 +8509,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8657,7 +8685,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8772,7 +8800,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,7 +8854,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8915,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8931,17 +8959,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8949,22 +8977,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -8997,12 +9025,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9016,47 +9044,852 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr">
         <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>3/15</t>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,22 +4476,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,22 +4591,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4944,17 +4944,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,22 +5063,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5182,22 +5182,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5301,22 +5301,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,22 +5539,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,22 +5892,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6011,22 +6011,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6130,17 +6130,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7078,17 +7078,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7197,22 +7197,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7316,22 +7316,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7554,22 +7554,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7976,12 +7976,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8083,24 +8083,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8192,32 +8192,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -8225,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8249,37 +8253,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8307,32 +8311,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8340,7 +8348,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8364,27 +8372,27 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8394,7 +8402,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8422,32 +8430,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -8455,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8479,37 +8491,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8537,32 +8549,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8570,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8594,37 +8610,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8652,32 +8668,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8685,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8709,32 +8729,32 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8767,32 +8787,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8800,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8824,37 +8848,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8882,32 +8906,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8915,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8939,37 +8967,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8997,32 +9025,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9030,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9054,32 +9086,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9112,32 +9144,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -9145,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9169,37 +9205,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9296,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9299,7 +9335,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9314,7 +9350,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9342,32 +9378,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9375,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9399,27 +9439,27 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9429,7 +9469,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9530,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9544,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9645,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9644,7 +9684,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9720,7 +9760,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9774,7 +9814,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9782,22 +9822,22 @@
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9830,12 +9870,12 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9849,47 +9889,1427 @@
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr">
         <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
           <t>17:42</t>
         </is>
       </c>
-      <c r="V80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="W81" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y80" s="2" t="inlineStr">
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Z81" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA81" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr">
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
         <is>
           <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,22 +3528,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,22 +4357,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,22 +5063,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,22 +5658,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5782,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6487,22 +6487,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6721,22 +6721,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,17 +6964,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7316,22 +7316,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,12 +7797,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8149,22 +8149,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,17 +8273,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8392,17 +8392,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8982,22 +8982,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9612,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9645,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9669,17 +9673,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9689,12 +9693,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9727,32 +9731,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9760,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9784,37 +9792,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9842,32 +9850,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -9875,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9899,17 +9911,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9919,17 +9931,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9957,32 +9969,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -9990,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10014,37 +10030,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10088,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -10105,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10129,17 +10149,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10149,12 +10169,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10187,32 +10207,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10220,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10244,17 +10268,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10264,17 +10288,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10374,7 +10398,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10450,7 +10474,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10489,7 +10513,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10565,7 +10589,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10619,7 +10643,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10647,32 +10671,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10680,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10704,37 +10732,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10910,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10949,7 +10977,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11025,7 +11053,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11140,7 +11168,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11202,22 +11230,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11250,12 +11278,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11304,12 +11332,817 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
           <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,17 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,12 +4715,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,17 +5068,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,17 +5425,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,17 +6611,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,17 +7321,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7678,17 +7678,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,17 +8987,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9693,17 +9693,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10671,36 +10671,32 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10708,7 +10704,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10732,17 +10728,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10752,17 +10748,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10790,32 +10786,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10823,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10847,17 +10847,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11020,32 +11020,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11053,7 +11057,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11077,17 +11081,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11097,12 +11101,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11135,32 +11139,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -11168,7 +11176,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11192,17 +11200,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11212,17 +11220,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11291,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11337,7 +11345,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11365,32 +11373,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11398,7 +11410,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11422,17 +11434,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11442,17 +11454,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11525,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11628,7 +11640,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11743,7 +11755,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11797,7 +11809,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11825,32 +11837,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11858,7 +11874,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11882,17 +11898,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11902,12 +11918,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -11920,22 +11936,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11968,12 +11984,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11987,7 +12003,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12017,17 +12033,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -12035,22 +12051,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12083,12 +12099,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12102,47 +12118,507 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
+      <c r="AB101" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
         </is>
       </c>
-      <c r="AC99" s="2" t="inlineStr">
+      <c r="AC101" s="2" t="inlineStr">
         <is>
           <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,17 +5068,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,17 +7321,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,17 +8273,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,17 +8987,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9225,12 +9225,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10169,17 +10169,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10748,17 +10748,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11383,24 +11383,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -11492,32 +11492,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11525,7 +11529,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11549,17 +11553,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11569,7 +11573,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11694,7 +11698,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11813,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11847,12 +11851,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -11874,7 +11878,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11923,7 +11927,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -11956,32 +11960,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -11989,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12013,17 +12021,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12033,17 +12041,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -12071,32 +12079,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -12104,7 +12116,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12128,17 +12140,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12148,17 +12160,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12186,32 +12198,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -12219,7 +12235,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12243,17 +12259,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12263,17 +12279,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -12301,32 +12317,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -12334,7 +12354,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12358,17 +12378,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12378,12 +12398,12 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12449,7 +12469,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12493,17 +12513,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12584,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12608,17 +12628,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-浦东78路.xlsx
+++ b/data/export/2026-10-11-浦东78路.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,17 +8273,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12327,24 +12327,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -12436,32 +12436,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -12469,7 +12473,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12493,17 +12497,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12513,17 +12517,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12588,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
